--- a/artfynd/A 36053-2024 artfynd.xlsx
+++ b/artfynd/A 36053-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796513</v>
+        <v>119796512</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454051</v>
+        <v>454181</v>
       </c>
       <c r="R5" t="n">
-        <v>6879770</v>
+        <v>6880010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796512</v>
+        <v>119796513</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454181</v>
+        <v>454051</v>
       </c>
       <c r="R6" t="n">
-        <v>6880010</v>
+        <v>6879770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36053-2024 artfynd.xlsx
+++ b/artfynd/A 36053-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796512</v>
+        <v>119796513</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454181</v>
+        <v>454051</v>
       </c>
       <c r="R5" t="n">
-        <v>6880010</v>
+        <v>6879770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796513</v>
+        <v>119796512</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454051</v>
+        <v>454181</v>
       </c>
       <c r="R6" t="n">
-        <v>6879770</v>
+        <v>6880010</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36053-2024 artfynd.xlsx
+++ b/artfynd/A 36053-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796513</v>
+        <v>119796512</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454051</v>
+        <v>454181</v>
       </c>
       <c r="R5" t="n">
-        <v>6879770</v>
+        <v>6880010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796512</v>
+        <v>119796513</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454181</v>
+        <v>454051</v>
       </c>
       <c r="R6" t="n">
-        <v>6880010</v>
+        <v>6879770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
